--- a/output/清洗后_实习练习-销售脏数据.xlsx
+++ b/output/清洗后_实习练习-销售脏数据.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,10 +454,15 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>销售额_previous</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>销售员</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>地区</t>
         </is>
@@ -473,8 +474,10 @@
           <t>SO20260001</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
-        <v>46236</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -495,12 +498,15 @@
       <c r="G2" t="n">
         <v>59990</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="n">
+        <v>59990</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -512,8 +518,10 @@
           <t>SO20260002</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
-        <v>46237</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -532,14 +540,17 @@
         <v>79</v>
       </c>
       <c r="G3" t="n">
+        <v>1580</v>
+      </c>
+      <c r="H3" t="n">
         <v>948</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>王芳</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>西南</t>
         </is>
@@ -551,11 +562,7 @@
           <t>SO20260003</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>日期格式错误</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>U盘128G</t>
@@ -575,12 +582,15 @@
       <c r="G4" t="n">
         <v>158</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="n">
+        <v>158</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -592,8 +602,10 @@
           <t>SO20260004</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
-        <v>46239</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -609,17 +621,20 @@
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>1299</v>
       </c>
       <c r="G5" t="n">
+        <v>2598</v>
+      </c>
+      <c r="H5" t="n">
         <v>3897</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>赵磊</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -631,8 +646,10 @@
           <t>SO20260005</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
-        <v>46240</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
@@ -647,14 +664,17 @@
         <v>559</v>
       </c>
       <c r="G6" t="n">
+        <v>6708</v>
+      </c>
+      <c r="H6" t="n">
         <v>559</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -666,8 +686,10 @@
           <t>SO20260006</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
-        <v>46210</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -686,14 +708,17 @@
         <v>5999</v>
       </c>
       <c r="G7" t="n">
+        <v>11998</v>
+      </c>
+      <c r="H7" t="n">
         <v>71988</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>赵磊</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -705,8 +730,10 @@
           <t>SO20260007</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
-        <v>46242</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -725,14 +752,17 @@
         <v>359</v>
       </c>
       <c r="G8" t="n">
+        <v>1077</v>
+      </c>
+      <c r="H8" t="n">
         <v>4308</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>王芳</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>西南</t>
         </is>
@@ -744,8 +774,10 @@
           <t>SO20260008</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
-        <v>46243</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -764,14 +796,17 @@
         <v>89</v>
       </c>
       <c r="G9" t="n">
+        <v>178</v>
+      </c>
+      <c r="H9" t="n">
         <v>-3599</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>李娜</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -783,8 +818,10 @@
           <t>SO20260009</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
-        <v>46213</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -803,14 +840,17 @@
         <v>1299</v>
       </c>
       <c r="G10" t="n">
+        <v>12990</v>
+      </c>
+      <c r="H10" t="n">
         <v>3897</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -822,8 +862,10 @@
           <t>SO20260010</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
-        <v>46245</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -842,14 +884,17 @@
         <v>89</v>
       </c>
       <c r="G11" t="n">
+        <v>1068</v>
+      </c>
+      <c r="H11" t="n">
         <v>89</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>赵磊</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -857,8 +902,10 @@
           <t>SO20260011</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
-        <v>46246</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -877,14 +924,17 @@
         <v>5999</v>
       </c>
       <c r="G12" t="n">
+        <v>59990</v>
+      </c>
+      <c r="H12" t="n">
         <v>11998</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>王芳</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -896,8 +946,10 @@
           <t>SO20260012</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
-        <v>46216</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -913,17 +965,20 @@
         <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>1299</v>
       </c>
       <c r="G13" t="n">
         <v>15588</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" t="n">
+        <v>15588</v>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>王芳</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -935,8 +990,10 @@
           <t>SO20260013</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
-        <v>46248</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -957,12 +1014,15 @@
       <c r="G14" t="n">
         <v>9980</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" t="n">
+        <v>9980</v>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>王芳</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -974,8 +1034,10 @@
           <t>SO20260014</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
-        <v>46249</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -994,14 +1056,17 @@
         <v>499</v>
       </c>
       <c r="G15" t="n">
+        <v>2495</v>
+      </c>
+      <c r="H15" t="n">
         <v>1497</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>李娜</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -1013,8 +1078,10 @@
           <t>SO20260015</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
-        <v>46219</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1033,14 +1100,17 @@
         <v>5999</v>
       </c>
       <c r="G16" t="n">
+        <v>17997</v>
+      </c>
+      <c r="H16" t="n">
         <v>29995</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>华南</t>
         </is>
@@ -1052,8 +1122,10 @@
           <t>SO20260016</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
-        <v>46251</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1072,10 +1144,13 @@
         <v>89</v>
       </c>
       <c r="G17" t="n">
+        <v>445</v>
+      </c>
+      <c r="H17" t="n">
         <v>178</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -1087,8 +1162,10 @@
           <t>SO20260017</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
-        <v>46252</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1107,14 +1184,17 @@
         <v>299</v>
       </c>
       <c r="G18" t="n">
+        <v>3588</v>
+      </c>
+      <c r="H18" t="n">
         <v>897</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>赵磊</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -1126,8 +1206,10 @@
           <t>SO20260018</t>
         </is>
       </c>
-      <c r="B19" s="1" t="n">
-        <v>46222</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1146,14 +1228,17 @@
         <v>359</v>
       </c>
       <c r="G19" t="n">
+        <v>1795</v>
+      </c>
+      <c r="H19" t="n">
         <v>7180</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>李娜</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>西南</t>
         </is>
@@ -1165,8 +1250,10 @@
           <t>SO20260019</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
-        <v>46254</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1178,21 +1265,30 @@
           <t>电脑整机</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>9999</v>
-      </c>
-      <c r="F20" t="n">
-        <v>5999</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>异常</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>异常</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>异常</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
         <v>29995</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>华南</t>
         </is>
@@ -1204,8 +1300,10 @@
           <t>SO20260020</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
-        <v>46255</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1224,14 +1322,17 @@
         <v>299</v>
       </c>
       <c r="G21" t="n">
+        <v>1495</v>
+      </c>
+      <c r="H21" t="n">
         <v>897</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -1243,8 +1344,10 @@
           <t>SO20260021</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
-        <v>46225</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1263,14 +1366,17 @@
         <v>1299</v>
       </c>
       <c r="G22" t="n">
+        <v>25980</v>
+      </c>
+      <c r="H22" t="n">
         <v>10392</v>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -1282,8 +1388,10 @@
           <t>SO20260022</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
-        <v>46257</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1302,14 +1410,17 @@
         <v>89</v>
       </c>
       <c r="G23" t="n">
+        <v>1780</v>
+      </c>
+      <c r="H23" t="n">
         <v>89</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -1321,8 +1432,10 @@
           <t>SO20260023</t>
         </is>
       </c>
-      <c r="B24" s="1" t="n">
-        <v>46258</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1340,13 +1453,16 @@
       <c r="F24" t="n">
         <v>499</v>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
+      <c r="G24" t="n">
+        <v>2495</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
         <is>
           <t>赵磊</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>西南</t>
         </is>
@@ -1358,8 +1474,10 @@
           <t>SO20260024</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
-        <v>46228</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1378,14 +1496,17 @@
         <v>79</v>
       </c>
       <c r="G25" t="n">
+        <v>948</v>
+      </c>
+      <c r="H25" t="n">
         <v>395</v>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -1397,8 +1518,10 @@
           <t>SO20260025</t>
         </is>
       </c>
-      <c r="B26" s="1" t="n">
-        <v>46260</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1417,14 +1540,17 @@
         <v>299</v>
       </c>
       <c r="G26" t="n">
+        <v>897</v>
+      </c>
+      <c r="H26" t="n">
         <v>3588</v>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>华南</t>
         </is>
@@ -1436,8 +1562,10 @@
           <t>SO20260026</t>
         </is>
       </c>
-      <c r="B27" s="1" t="n">
-        <v>46261</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1456,14 +1584,17 @@
         <v>499</v>
       </c>
       <c r="G27" t="n">
+        <v>9980</v>
+      </c>
+      <c r="H27" t="n">
         <v>1497</v>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -1475,8 +1606,10 @@
           <t>SO20260027</t>
         </is>
       </c>
-      <c r="B28" s="1" t="n">
-        <v>46231</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1495,14 +1628,17 @@
         <v>79</v>
       </c>
       <c r="G28" t="n">
+        <v>237</v>
+      </c>
+      <c r="H28" t="n">
         <v>948</v>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -1514,8 +1650,10 @@
           <t>SO20260028</t>
         </is>
       </c>
-      <c r="B29" s="1" t="n">
-        <v>46235</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1534,14 +1672,17 @@
         <v>299</v>
       </c>
       <c r="G29" t="n">
+        <v>299</v>
+      </c>
+      <c r="H29" t="n">
         <v>-129</v>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>华南</t>
         </is>
@@ -1553,8 +1694,10 @@
           <t>SO20260029</t>
         </is>
       </c>
-      <c r="B30" s="1" t="n">
-        <v>46236</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1573,14 +1716,17 @@
         <v>499</v>
       </c>
       <c r="G30" t="n">
+        <v>5988</v>
+      </c>
+      <c r="H30" t="n">
         <v>998</v>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>赵磊</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>西南</t>
         </is>
@@ -1592,8 +1738,10 @@
           <t>SO20260030</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n">
-        <v>46206</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1612,14 +1760,17 @@
         <v>559</v>
       </c>
       <c r="G31" t="n">
+        <v>1118</v>
+      </c>
+      <c r="H31" t="n">
         <v>6708</v>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>赵磊</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -1631,8 +1782,10 @@
           <t>SO20260031</t>
         </is>
       </c>
-      <c r="B32" s="1" t="n">
-        <v>46238</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1651,14 +1804,17 @@
         <v>5999</v>
       </c>
       <c r="G32" t="n">
+        <v>119980</v>
+      </c>
+      <c r="H32" t="n">
         <v>11998</v>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>王芳</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -1670,8 +1826,10 @@
           <t>SO20260032</t>
         </is>
       </c>
-      <c r="B33" s="1" t="n">
-        <v>46239</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1689,13 +1847,16 @@
       <c r="F33" t="n">
         <v>559</v>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
+      <c r="G33" t="n">
+        <v>1677</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
         <is>
           <t>李娜</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -1707,8 +1868,10 @@
           <t>SO20260033</t>
         </is>
       </c>
-      <c r="B34" s="1" t="n">
-        <v>46209</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1727,14 +1890,17 @@
         <v>1299</v>
       </c>
       <c r="G34" t="n">
+        <v>15588</v>
+      </c>
+      <c r="H34" t="n">
         <v>1299</v>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>西南</t>
         </is>
@@ -1746,8 +1912,10 @@
           <t>SO20260034</t>
         </is>
       </c>
-      <c r="B35" s="1" t="n">
-        <v>46241</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1766,14 +1934,17 @@
         <v>559</v>
       </c>
       <c r="G35" t="n">
+        <v>6708</v>
+      </c>
+      <c r="H35" t="n">
         <v>11180</v>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -1785,8 +1956,10 @@
           <t>SO20260035</t>
         </is>
       </c>
-      <c r="B36" s="1" t="n">
-        <v>46242</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1805,14 +1978,17 @@
         <v>5999</v>
       </c>
       <c r="G36" t="n">
+        <v>17997</v>
+      </c>
+      <c r="H36" t="n">
         <v>11998</v>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -1824,8 +2000,10 @@
           <t>SO20260036</t>
         </is>
       </c>
-      <c r="B37" s="1" t="n">
-        <v>46212</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1837,21 +2015,30 @@
           <t>外设</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>异常</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>异常</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>异常</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
         <v>712</v>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -1863,8 +2050,10 @@
           <t>SO20260037</t>
         </is>
       </c>
-      <c r="B38" s="1" t="n">
-        <v>46244</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1883,14 +2072,17 @@
         <v>359</v>
       </c>
       <c r="G38" t="n">
+        <v>7180</v>
+      </c>
+      <c r="H38" t="n">
         <v>4308</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -1902,11 +2094,7 @@
           <t>SO20260038</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>高清摄像头</t>
@@ -1926,12 +2114,15 @@
       <c r="G39" t="n">
         <v>3588</v>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" t="n">
+        <v>3588</v>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -1943,8 +2134,10 @@
           <t>SO20260039</t>
         </is>
       </c>
-      <c r="B40" s="1" t="n">
-        <v>46215</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1963,14 +2156,17 @@
         <v>359</v>
       </c>
       <c r="G40" t="n">
+        <v>1077</v>
+      </c>
+      <c r="H40" t="n">
         <v>718</v>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>华南</t>
         </is>
@@ -1982,8 +2178,10 @@
           <t>SO20260040</t>
         </is>
       </c>
-      <c r="B41" s="1" t="n">
-        <v>46247</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1999,17 +2197,20 @@
         <v>10</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>1299</v>
       </c>
       <c r="G41" t="n">
         <v>12990</v>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" t="n">
+        <v>12990</v>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>华南</t>
         </is>
@@ -2021,8 +2222,10 @@
           <t>SO20260041</t>
         </is>
       </c>
-      <c r="B42" s="1" t="n">
-        <v>46248</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2037,14 +2240,17 @@
         <v>299</v>
       </c>
       <c r="G42" t="n">
+        <v>1495</v>
+      </c>
+      <c r="H42" t="n">
         <v>2392</v>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -2056,8 +2262,10 @@
           <t>SO20260042</t>
         </is>
       </c>
-      <c r="B43" s="1" t="n">
-        <v>46218</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2076,14 +2284,17 @@
         <v>299</v>
       </c>
       <c r="G43" t="n">
+        <v>5980</v>
+      </c>
+      <c r="H43" t="n">
         <v>2990</v>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>西南</t>
         </is>
@@ -2095,8 +2306,10 @@
           <t>SO20260043</t>
         </is>
       </c>
-      <c r="B44" s="1" t="n">
-        <v>46250</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2115,14 +2328,17 @@
         <v>499</v>
       </c>
       <c r="G44" t="n">
+        <v>3992</v>
+      </c>
+      <c r="H44" t="n">
         <v>998</v>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>赵磊</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -2134,8 +2350,10 @@
           <t>SO20260044</t>
         </is>
       </c>
-      <c r="B45" s="1" t="n">
-        <v>46251</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2154,14 +2372,17 @@
         <v>79</v>
       </c>
       <c r="G45" t="n">
+        <v>237</v>
+      </c>
+      <c r="H45" t="n">
         <v>632</v>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -2173,8 +2394,10 @@
           <t>SO20260045</t>
         </is>
       </c>
-      <c r="B46" s="1" t="n">
-        <v>46221</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2193,14 +2416,17 @@
         <v>1299</v>
       </c>
       <c r="G46" t="n">
+        <v>10392</v>
+      </c>
+      <c r="H46" t="n">
         <v>3897</v>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -2212,8 +2438,10 @@
           <t>SO20260046</t>
         </is>
       </c>
-      <c r="B47" s="1" t="n">
-        <v>46253</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2232,14 +2460,17 @@
         <v>5999</v>
       </c>
       <c r="G47" t="n">
+        <v>29995</v>
+      </c>
+      <c r="H47" t="n">
         <v>17997</v>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>李娜</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -2251,8 +2482,10 @@
           <t>SO20260047</t>
         </is>
       </c>
-      <c r="B48" s="1" t="n">
-        <v>46254</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2271,14 +2504,17 @@
         <v>299</v>
       </c>
       <c r="G48" t="n">
+        <v>5980</v>
+      </c>
+      <c r="H48" t="n">
         <v>3588</v>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>李娜</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -2290,8 +2526,10 @@
           <t>SO20260048</t>
         </is>
       </c>
-      <c r="B49" s="1" t="n">
-        <v>46224</v>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2310,14 +2548,17 @@
         <v>79</v>
       </c>
       <c r="G49" t="n">
+        <v>790</v>
+      </c>
+      <c r="H49" t="n">
         <v>79</v>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>李娜</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>华南</t>
         </is>
@@ -2329,8 +2570,10 @@
           <t>SO20260049</t>
         </is>
       </c>
-      <c r="B50" s="1" t="n">
-        <v>46256</v>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2349,14 +2592,17 @@
         <v>499</v>
       </c>
       <c r="G50" t="n">
+        <v>5988</v>
+      </c>
+      <c r="H50" t="n">
         <v>499</v>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -2368,8 +2614,10 @@
           <t>SO20260050</t>
         </is>
       </c>
-      <c r="B51" s="1" t="n">
-        <v>46257</v>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2388,14 +2636,17 @@
         <v>359</v>
       </c>
       <c r="G51" t="n">
+        <v>2872</v>
+      </c>
+      <c r="H51" t="n">
         <v>359</v>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -2407,8 +2658,10 @@
           <t>SO20260051</t>
         </is>
       </c>
-      <c r="B52" s="1" t="n">
-        <v>46227</v>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2420,21 +2673,30 @@
           <t>存储</t>
         </is>
       </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>79</v>
-      </c>
-      <c r="G52" t="n">
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>异常</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>异常</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>异常</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
         <v>395</v>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -2446,8 +2708,10 @@
           <t>SO20260052</t>
         </is>
       </c>
-      <c r="B53" s="1" t="n">
-        <v>46259</v>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2466,14 +2730,17 @@
         <v>559</v>
       </c>
       <c r="G53" t="n">
+        <v>5590</v>
+      </c>
+      <c r="H53" t="n">
         <v>1677</v>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -2485,8 +2752,10 @@
           <t>SO20260053</t>
         </is>
       </c>
-      <c r="B54" s="1" t="n">
-        <v>46260</v>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2505,14 +2774,17 @@
         <v>499</v>
       </c>
       <c r="G54" t="n">
+        <v>9980</v>
+      </c>
+      <c r="H54" t="n">
         <v>5988</v>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>华南</t>
         </is>
@@ -2524,8 +2796,10 @@
           <t>SO20260054</t>
         </is>
       </c>
-      <c r="B55" s="1" t="n">
-        <v>46230</v>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2544,14 +2818,17 @@
         <v>1299</v>
       </c>
       <c r="G55" t="n">
+        <v>12990</v>
+      </c>
+      <c r="H55" t="n">
         <v>2598</v>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>西南</t>
         </is>
@@ -2563,8 +2840,10 @@
           <t>SO20260055</t>
         </is>
       </c>
-      <c r="B56" s="1" t="n">
-        <v>46262</v>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2583,14 +2862,17 @@
         <v>559</v>
       </c>
       <c r="G56" t="n">
+        <v>1118</v>
+      </c>
+      <c r="H56" t="n">
         <v>1677</v>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>华南</t>
         </is>
@@ -2602,8 +2884,10 @@
           <t>SO20260056</t>
         </is>
       </c>
-      <c r="B57" s="1" t="n">
-        <v>46235</v>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2624,12 +2908,15 @@
       <c r="G57" t="n">
         <v>4308</v>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" t="n">
+        <v>4308</v>
+      </c>
+      <c r="I57" t="inlineStr">
         <is>
           <t>李娜</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -2641,8 +2928,10 @@
           <t>SO20260057</t>
         </is>
       </c>
-      <c r="B58" s="1" t="n">
-        <v>46205</v>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2661,14 +2950,17 @@
         <v>5999</v>
       </c>
       <c r="G58" t="n">
+        <v>71988</v>
+      </c>
+      <c r="H58" t="n">
         <v>29995</v>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -2680,8 +2972,10 @@
           <t>SO20260058</t>
         </is>
       </c>
-      <c r="B59" s="1" t="n">
-        <v>46237</v>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -2700,14 +2994,17 @@
         <v>79</v>
       </c>
       <c r="G59" t="n">
+        <v>158</v>
+      </c>
+      <c r="H59" t="n">
         <v>948</v>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -2719,8 +3016,10 @@
           <t>SO20260059</t>
         </is>
       </c>
-      <c r="B60" s="1" t="n">
-        <v>46238</v>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2739,14 +3038,17 @@
         <v>89</v>
       </c>
       <c r="G60" t="n">
+        <v>712</v>
+      </c>
+      <c r="H60" t="n">
         <v>445</v>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -2758,8 +3060,10 @@
           <t>SO20260060</t>
         </is>
       </c>
-      <c r="B61" s="1" t="n">
-        <v>46208</v>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -2775,17 +3079,20 @@
         <v>8</v>
       </c>
       <c r="F61" t="n">
-        <v>5</v>
+        <v>5999</v>
       </c>
       <c r="G61" t="n">
+        <v>47992</v>
+      </c>
+      <c r="H61" t="n">
         <v>17997</v>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>华东</t>
         </is>
@@ -2797,8 +3104,10 @@
           <t>SO20260061</t>
         </is>
       </c>
-      <c r="B62" s="1" t="n">
-        <v>46240</v>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2817,14 +3126,17 @@
         <v>79</v>
       </c>
       <c r="G62" t="n">
+        <v>632</v>
+      </c>
+      <c r="H62" t="n">
         <v>395</v>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -2836,8 +3148,10 @@
           <t>SO20260062</t>
         </is>
       </c>
-      <c r="B63" s="1" t="n">
-        <v>46241</v>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2856,14 +3170,17 @@
         <v>559</v>
       </c>
       <c r="G63" t="n">
+        <v>1118</v>
+      </c>
+      <c r="H63" t="n">
         <v>4472</v>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>王芳</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -2875,8 +3192,10 @@
           <t>SO20260063</t>
         </is>
       </c>
-      <c r="B64" s="1" t="n">
-        <v>46211</v>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2895,14 +3214,17 @@
         <v>89</v>
       </c>
       <c r="G64" t="n">
+        <v>1780</v>
+      </c>
+      <c r="H64" t="n">
         <v>178</v>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>王芳</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>华北</t>
         </is>
@@ -2914,8 +3236,10 @@
           <t>SO20260064</t>
         </is>
       </c>
-      <c r="B65" s="1" t="n">
-        <v>46243</v>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2931,17 +3255,20 @@
         <v>12</v>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>5999</v>
       </c>
       <c r="G65" t="n">
+        <v>71988</v>
+      </c>
+      <c r="H65" t="n">
         <v>11998</v>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>赵磊</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>西南</t>
         </is>
@@ -2953,8 +3280,10 @@
           <t>SO20260065</t>
         </is>
       </c>
-      <c r="B66" s="1" t="n">
-        <v>46244</v>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2973,14 +3302,17 @@
         <v>89</v>
       </c>
       <c r="G66" t="n">
+        <v>712</v>
+      </c>
+      <c r="H66" t="n">
         <v>267</v>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>华中</t>
         </is>
@@ -2992,8 +3324,10 @@
           <t>SO20260020</t>
         </is>
       </c>
-      <c r="B67" s="1" t="n">
-        <v>46225</v>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3012,14 +3346,17 @@
         <v>1299</v>
       </c>
       <c r="G67" t="n">
+        <v>25980</v>
+      </c>
+      <c r="H67" t="n">
         <v>10392</v>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>陈静</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>华南</t>
         </is>
